--- a/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Agenda_Aug_2022_Checklist.xlsx
+++ b/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Agenda_Aug_2022_Checklist.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/todd/Documents/Work/Communications/Workshops/2022-08-16 CE-QUAL-W2 Workshop/_Agenda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/todd/Documents/Work/Communications/Workshops/2022-08-16 CE-QUAL-W2 Workshop/__Agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C567D70-14AD-2947-96DE-64E5B5BEE925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED69DE6-9292-E440-833C-488D2311A59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{7D882646-A55C-4A5C-840E-5C8671CF37BB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="58">
   <si>
     <t>Instructor</t>
   </si>
@@ -202,6 +202,15 @@
   </si>
   <si>
     <t>Number</t>
+  </si>
+  <si>
+    <t>Zhong?</t>
+  </si>
+  <si>
+    <t>Isaac?</t>
+  </si>
+  <si>
+    <t>Barry?</t>
   </si>
 </sst>
 </file>
@@ -351,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -440,34 +449,31 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,18 +820,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="31" t="s">
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="32" t="s">
+      <c r="L1" s="38"/>
+      <c r="M1" s="30" t="s">
         <v>47</v>
       </c>
     </row>
@@ -890,8 +896,8 @@
       <c r="F3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="36" t="s">
-        <v>27</v>
+      <c r="G3" s="34" t="s">
+        <v>53</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
@@ -918,8 +924,8 @@
       <c r="F4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="37" t="s">
-        <v>27</v>
+      <c r="G4" s="35" t="s">
+        <v>53</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
@@ -1064,10 +1070,10 @@
         <v>48</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>23</v>
@@ -1099,15 +1105,15 @@
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33" t="s">
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="33" t="s">
+      <c r="I10" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="J10" s="31" t="s">
         <v>41</v>
       </c>
       <c r="K10" s="7" t="s">
@@ -1163,10 +1169,8 @@
       <c r="E12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="33"/>
-      <c r="G12" s="38" t="s">
-        <v>27</v>
-      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
@@ -1188,16 +1192,16 @@
       <c r="D13" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
     </row>
     <row r="14" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18">
@@ -1210,9 +1214,11 @@
         <v>33</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="11"/>
+        <v>55</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>56</v>
+      </c>
       <c r="F14" s="11" t="s">
         <v>23</v>
       </c>
@@ -1269,7 +1275,7 @@
         <v>13</v>
       </c>
       <c r="E16" s="7"/>
-      <c r="F16" s="33"/>
+      <c r="F16" s="31"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -1290,9 +1296,11 @@
         <v>6</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="11"/>
+        <v>56</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
@@ -1321,7 +1329,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="33"/>
+      <c r="F18" s="31"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -1345,7 +1353,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="36" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="11" t="s">
@@ -1373,7 +1381,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="7"/>
-      <c r="F20" s="33"/>
+      <c r="F20" s="31"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -1429,7 +1437,7 @@
       <c r="E22" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="33"/>
+      <c r="F22" s="31"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -1514,7 +1522,7 @@
       <c r="F25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="37" t="s">
+      <c r="G25" s="35" t="s">
         <v>53</v>
       </c>
       <c r="H25" s="11"/>
@@ -1563,7 +1571,7 @@
         <v>17</v>
       </c>
       <c r="E27" s="28"/>
-      <c r="F27" s="35"/>
+      <c r="F27" s="33"/>
       <c r="G27" s="28" t="s">
         <v>20</v>
       </c>
@@ -1592,7 +1600,7 @@
       <c r="F28" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G28" s="37" t="s">
+      <c r="G28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="H28" s="11"/>
@@ -1639,7 +1647,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="28"/>
-      <c r="F30" s="35"/>
+      <c r="F30" s="33"/>
       <c r="G30" s="28" t="s">
         <v>53</v>
       </c>
@@ -1668,7 +1676,7 @@
       <c r="F31" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G31" s="37" t="s">
+      <c r="G31" s="35" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="11"/>
@@ -1744,7 +1752,7 @@
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="29"/>
-      <c r="G34" s="37" t="s">
+      <c r="G34" s="35" t="s">
         <v>27</v>
       </c>
       <c r="H34" s="9"/>
